--- a/site/exports/scu-math.xlsx
+++ b/site/exports/scu-math.xlsx
@@ -734,7 +734,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -795,7 +795,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L3" s="2" t="b">
@@ -862,7 +862,7 @@
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L4" s="2" t="b">
